--- a/web/Pipistrelli 2023.xlsx
+++ b/web/Pipistrelli 2023.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,7 +506,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Piazza del Castello</t>
@@ -546,10 +545,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -562,7 +560,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Via San Leonardo Murialdo 21</t>
@@ -573,7 +570,11 @@
           <t>Villaverla</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>45.6499676</v>
       </c>
@@ -598,10 +599,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -614,7 +614,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Via San Francesco</t>
@@ -625,7 +624,11 @@
           <t>Montebello vicentino</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>45.4596014</v>
       </c>
@@ -650,10 +653,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -666,7 +668,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Via San Rocco 27</t>
@@ -677,7 +678,11 @@
           <t>Monte di Malo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>45.6619177</v>
       </c>
@@ -702,10 +707,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45003</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -718,7 +722,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Via Risorgimento 46</t>
@@ -758,10 +761,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45003</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -774,7 +776,6 @@
           <t>Rhinolophus ferrumequinum</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Lumignano</t>
@@ -785,7 +786,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.45985</v>
       </c>
@@ -810,10 +815,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -826,7 +830,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Ferrovieri</t>
@@ -866,10 +869,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45014</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -882,7 +884,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Via Aldo Moro</t>
@@ -893,7 +894,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>45.661886</v>
       </c>
@@ -918,10 +923,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45045</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -934,7 +938,6 @@
           <t>Plecotus auritus</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Via Regina Margherita</t>
@@ -974,10 +977,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45057</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -990,7 +992,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Via Roma</t>
@@ -1001,7 +1002,11 @@
           <t>Zovencedo</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>45.4300235</v>
       </c>
@@ -1026,10 +1031,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1042,7 +1046,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1082,10 +1085,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1098,7 +1100,6 @@
           <t>Nyctalus leisleri</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Via Fioretta 8</t>
@@ -1138,10 +1139,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1154,7 +1154,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Via delle Fornaci 72</t>
@@ -1194,10 +1193,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45080</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1210,7 +1208,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Via Guglielmo Marconi</t>
@@ -1221,7 +1218,11 @@
           <t>Valli del Pasubio</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>45.7398938</v>
       </c>
@@ -1246,10 +1247,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45084</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1262,7 +1262,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Via Corvo 62</t>
@@ -1273,7 +1272,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>45.6403</v>
       </c>
@@ -1298,10 +1301,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1314,7 +1316,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Via Sila 3</t>
@@ -1325,7 +1326,11 @@
           <t>Schiavon</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>45.6777651</v>
       </c>
@@ -1350,10 +1355,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1366,7 +1370,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Via Sacchi Bortolo, 32</t>
@@ -1406,10 +1409,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1422,7 +1424,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Via Sacchi Bortolo, 32</t>
@@ -1462,10 +1463,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45102</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1478,7 +1478,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1518,10 +1517,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45102</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1534,7 +1532,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Via Monte Novegno</t>
@@ -1545,7 +1542,11 @@
           <t>Isola Vicentina</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>45.6299029</v>
       </c>
@@ -1575,7 +1576,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1588,7 +1589,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Fara Vicentino</t>
@@ -1599,7 +1599,11 @@
           <t>Fara Vicentino</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>45.7395927</v>
       </c>
@@ -1614,16 +1618,14 @@
       <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1636,7 +1638,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>via Tavernelle 9</t>
@@ -1666,16 +1667,14 @@
       <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1688,7 +1687,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>San Giorgio di Perlena</t>
@@ -1699,7 +1697,6 @@
           <t>San Giorgio di Perlena</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>45.7304755</v>
       </c>
@@ -1714,16 +1711,14 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1736,7 +1731,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>via Revoloni 24</t>
@@ -1747,7 +1741,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>45.6285174</v>
       </c>
@@ -1772,10 +1770,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1788,7 +1785,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>via Lago di Vico 60</t>
@@ -1818,16 +1814,14 @@
       <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45104</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1840,7 +1834,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>via Da Vinci 32</t>
@@ -1870,16 +1863,14 @@
       <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45104</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1892,7 +1883,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>via Silvio Pellico</t>
@@ -1903,7 +1893,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>45.4318813</v>
       </c>
@@ -1928,10 +1922,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45104</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1944,7 +1937,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>via Vespucci 11</t>
@@ -1984,10 +1976,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2000,7 +1991,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Via Don Zilotto</t>
@@ -2040,10 +2030,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2056,7 +2045,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Chiampo</t>
@@ -2067,7 +2055,11 @@
           <t>Chiampo</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>45.5445732</v>
       </c>
@@ -2082,16 +2074,14 @@
       <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2104,7 +2094,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Via Monte Ortigara</t>
@@ -2115,7 +2104,11 @@
           <t>Valbrenta</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>45.8241443</v>
       </c>
@@ -2130,16 +2123,14 @@
       <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2152,7 +2143,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2163,7 +2153,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>45.4709699</v>
       </c>
@@ -2188,10 +2182,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2204,7 +2197,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -2215,7 +2207,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>45.5004723</v>
       </c>
@@ -2240,10 +2236,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2256,7 +2251,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Ospedale Civile di Vicenza San Bortolo</t>
@@ -2296,10 +2290,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2312,7 +2305,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Bolzano Vicentino</t>
@@ -2342,16 +2334,14 @@
       <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2364,7 +2354,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile 18/5</t>
@@ -2404,10 +2393,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2420,7 +2408,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Via Mazzini 27</t>
@@ -2431,7 +2418,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>45.4517637</v>
       </c>
@@ -2456,10 +2447,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2472,7 +2462,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2502,16 +2491,14 @@
       <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45109</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2524,7 +2511,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Grumolo delle Abbadesse</t>
@@ -2535,7 +2521,11 @@
           <t>Grumolo delle Abbadesse</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>45.5163094</v>
       </c>
@@ -2550,16 +2540,14 @@
       <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45109</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2572,7 +2560,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Spianzana</t>
@@ -2583,7 +2570,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>45.48688</v>
       </c>
@@ -2608,10 +2599,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2624,7 +2614,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Sarego</t>
@@ -2635,7 +2624,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>45.4081213</v>
       </c>
@@ -2660,10 +2653,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2676,7 +2668,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>via Europa 119</t>
@@ -2687,7 +2678,11 @@
           <t>Monticello Conte Otto</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>45.5925277</v>
       </c>
@@ -2712,10 +2707,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45111</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2728,7 +2722,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2773,7 +2766,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45111</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2786,7 +2779,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>via Molini 50a</t>
@@ -2826,10 +2818,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45112</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2842,7 +2833,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Via Mon Signor Pertile 18/5</t>
@@ -2882,10 +2872,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45112</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2898,7 +2887,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -2938,13 +2926,12 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45113</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>22.525</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2952,7 +2939,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -2963,7 +2949,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>45.7201187</v>
       </c>
@@ -2993,7 +2983,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3006,7 +2996,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Via Giacomo Zanella 71 A</t>
@@ -3017,7 +3006,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>45.7056839</v>
       </c>
@@ -3042,10 +3035,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3058,7 +3050,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3088,16 +3079,14 @@
       <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3110,7 +3099,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Strada delle Cattane 71</t>
@@ -3150,10 +3138,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45115</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3166,7 +3153,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Sarego</t>
@@ -3177,7 +3163,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>45.4081213</v>
       </c>
@@ -3202,10 +3192,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45115</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3218,7 +3207,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve"> contrà motton pusterla 2</t>
@@ -3258,10 +3246,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45115</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3274,7 +3261,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -3285,7 +3271,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>45.7201187</v>
       </c>
@@ -3315,7 +3305,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45116</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3328,7 +3318,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Contra Porta Padova, 46</t>
@@ -3358,16 +3347,14 @@
       <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45116</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3380,7 +3367,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Via Abruzzo 2</t>
@@ -3420,10 +3406,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45116</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3436,7 +3421,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Camisano Vicentino</t>
@@ -3447,7 +3431,11 @@
           <t>Camisano Vicentino</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>45.5220266</v>
       </c>
@@ -3462,16 +3450,14 @@
       <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3484,7 +3470,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>via Monsignor Pertile 19/23</t>
@@ -3524,10 +3509,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3540,7 +3524,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Santa Bertilla</t>
@@ -3585,7 +3568,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3598,7 +3581,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Contrà della Misericordia 24</t>
@@ -3638,10 +3620,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3654,7 +3635,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Via Industria 57</t>
@@ -3665,7 +3645,6 @@
           <t>Due Ville</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>45.8144577</v>
       </c>
@@ -3695,7 +3674,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3708,7 +3687,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>via Sabbionara 1</t>
@@ -3719,7 +3697,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>45.6355174</v>
       </c>
@@ -3744,10 +3726,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3760,7 +3741,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -3800,10 +3780,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3816,7 +3795,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Montebello Vicentino</t>
@@ -3827,7 +3805,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>45.4572159</v>
       </c>
@@ -3852,10 +3834,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45118</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3868,7 +3849,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>via Armedola 4 Lanze'</t>
@@ -3879,7 +3859,11 @@
           <t>Campiglia dei Berici</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>45.3362423</v>
       </c>
@@ -3904,10 +3888,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45120</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3920,7 +3903,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Quinto Vicentino</t>
@@ -3960,10 +3942,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3976,7 +3957,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Via Botticelli 6</t>
@@ -4016,10 +3996,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4032,7 +4011,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Strada Ca' Balbi</t>
@@ -4072,10 +4050,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45122</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4088,7 +4065,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Via Villa Beltrame 6</t>
@@ -4128,10 +4104,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45122</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4144,7 +4119,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Osteria Veneto's, 56, Corso Andrea Palladio</t>
@@ -4189,7 +4163,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4202,7 +4176,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4242,10 +4215,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4258,7 +4230,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>strada del Molino 10</t>
@@ -4298,10 +4269,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45125</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4314,7 +4284,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Via Giacomo Zanella</t>
@@ -4325,7 +4294,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>45.7034884</v>
       </c>
@@ -4350,10 +4323,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45125</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4366,7 +4338,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Viale Margherita vicino allo stadio</t>
@@ -4377,7 +4348,11 @@
           <t>Calvene</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>45.7659086</v>
       </c>
@@ -4402,10 +4377,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4418,7 +4392,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Via Marco Polo</t>
@@ -4458,10 +4431,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4474,7 +4446,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Stradone Fedele Lampertico</t>
@@ -4485,7 +4456,11 @@
           <t>Montegaldella</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>45.430864</v>
       </c>
@@ -4510,10 +4485,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4526,7 +4500,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Via Silvio Pellico</t>
@@ -4537,7 +4510,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>45.6641897</v>
       </c>
@@ -4562,10 +4539,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4578,7 +4554,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -4618,10 +4593,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4634,7 +4608,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Via Tintoretto 5</t>
@@ -4674,10 +4647,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45129</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4690,7 +4662,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Largo Europa 1</t>
@@ -4701,7 +4672,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>45.6585696</v>
       </c>
@@ -4726,10 +4701,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4742,7 +4716,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Viale Francesco Crispi 142</t>
@@ -4782,10 +4755,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4798,7 +4770,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4828,16 +4799,14 @@
       <c r="K82" t="n">
         <v>1</v>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4850,7 +4819,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -4880,16 +4848,14 @@
       <c r="K83" t="n">
         <v>1</v>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4902,7 +4868,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -4913,7 +4878,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>45.5004723</v>
       </c>
@@ -4938,10 +4907,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4954,7 +4922,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Strada della pilla 25A</t>
@@ -4965,7 +4932,6 @@
           <t>Zané</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>45.7201187</v>
       </c>
@@ -4990,10 +4956,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5006,7 +4971,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Via Ca Montanare 3</t>
@@ -5017,7 +4981,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>45.4721218</v>
       </c>
@@ -5032,16 +5000,14 @@
       <c r="K86" t="n">
         <v>1</v>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5054,7 +5020,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Ceroni, 37</t>
@@ -5094,10 +5059,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45137</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5110,7 +5074,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Via Ceroni, 37</t>
@@ -5150,10 +5113,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5166,7 +5128,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>viale Trenti 66</t>
@@ -5177,7 +5138,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>45.4437746</v>
       </c>
@@ -5192,16 +5157,14 @@
       <c r="K89" t="n">
         <v>1</v>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5214,7 +5177,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Zemola 16</t>
@@ -5225,7 +5187,11 @@
           <t>Cogollo del Cengio</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>45.7852211</v>
       </c>
@@ -5250,10 +5216,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45144</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5266,7 +5231,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Barbarno Mossano</t>
@@ -5296,16 +5260,14 @@
       <c r="K91" t="n">
         <v>1</v>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45155</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5318,7 +5280,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Via Martin Luther King 39e</t>
@@ -5358,10 +5319,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45155</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5374,7 +5334,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -5385,7 +5344,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>45.7244163</v>
       </c>
@@ -5400,16 +5363,14 @@
       <c r="K93" t="n">
         <v>1</v>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45161</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5422,7 +5383,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Via Roma 8</t>
@@ -5462,10 +5422,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45162</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -5478,7 +5437,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Via Giuseppe Zampieri 4</t>
@@ -5489,7 +5447,11 @@
           <t>Alonte</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>45.3650367</v>
       </c>
@@ -5514,10 +5476,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45165</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -5530,7 +5491,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Via Cavour 77</t>
@@ -5541,7 +5501,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>45.4612318</v>
       </c>
@@ -5566,10 +5530,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -5582,7 +5545,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Viale Riviera Berica 699</t>
@@ -5622,10 +5584,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -5638,7 +5599,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -5678,10 +5638,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45174</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -5694,7 +5653,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Via Boito 19</t>
@@ -5705,7 +5663,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>45.5004723</v>
       </c>
@@ -5730,10 +5692,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -5746,7 +5707,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Torri di Arcugnano</t>
@@ -5757,7 +5717,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>45.4930641</v>
       </c>
@@ -5782,10 +5746,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -5798,7 +5761,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Stazione di Vicenza, 21</t>
@@ -5838,10 +5800,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45179</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -5854,7 +5815,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Asiago</t>
@@ -5865,7 +5825,11 @@
           <t>Asiago</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>45.8753771</v>
       </c>
@@ -5890,10 +5854,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -5906,7 +5869,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>via Pasquali Marana 33</t>
@@ -5946,10 +5908,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -5962,7 +5923,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Via Andrea Mantegna 7</t>
@@ -5973,7 +5933,11 @@
           <t>Piazzola sul Brenta</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>45.5797865</v>
       </c>
@@ -5998,10 +5962,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45190</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6014,7 +5977,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Cappuccini 65</t>
@@ -6025,7 +5987,11 @@
           <t>Tezze sul Brenta</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>45.6861778</v>
       </c>
@@ -6050,10 +6016,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45190</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6066,7 +6031,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -6106,10 +6070,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45192</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6122,7 +6085,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Via Arturo Ferrarin 138</t>
@@ -6162,10 +6124,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6178,7 +6139,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6218,10 +6178,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6234,7 +6193,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -6274,10 +6232,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45245</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6290,7 +6247,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Via Lago Maggiore 1</t>
@@ -6301,7 +6257,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>45.5004723</v>
       </c>
@@ -6326,10 +6286,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45276</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -6342,7 +6301,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Via Pietro Scalcerle, 5</t>
@@ -6382,10 +6340,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45281</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -6398,7 +6355,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Contrà Barche, 40</t>
@@ -6438,7 +6394,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/web/Pipistrelli 2023.xlsx
+++ b/web/Pipistrelli 2023.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di Malo</t>
+          <t>Monte di malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del Pasubio</t>
+          <t>Valli del pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola Vicentina</t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara Vicentino</t>
+          <t>Fara vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano Vicentino</t>
+          <t>Bolzano vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle Abbadesse</t>
+          <t>Grumolo delle abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio Maggiore</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3642,14 +3642,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Due Ville</t>
+          <t>Dueville</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>VI</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>45.8144577</v>
+        <v>45.5479</v>
       </c>
       <c r="I61" t="n">
-        <v>15.9798551</v>
+        <v>11.5446</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3856,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei Berici</t>
+          <t>Campiglia dei berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3910,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto Vicentino</t>
+          <t>Quinto vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4723,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4826,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5174,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del Cengio</t>
+          <t>Cogollo del cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5915,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul Brenta</t>
+          <t>Piazzola sul brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul Brenta</t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/web/Pipistrelli 2023.xlsx
+++ b/web/Pipistrelli 2023.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di malo</t>
+          <t>Monte Di Malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del pasubio</t>
+          <t>Valli Del Pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara vicentino</t>
+          <t>Fara Vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano vicentino</t>
+          <t>Bolzano Vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle abbadesse</t>
+          <t>Grumolo Delle Abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei berici</t>
+          <t>Campiglia Dei Berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto vicentino</t>
+          <t>Quinto Vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del cengio</t>
+          <t>Cogollo Del Cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul brenta</t>
+          <t>Piazzola Sul Brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
